--- a/data/trans_orig/P1402-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1402-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2007</t>
+          <t>Población con diagnóstico de diabetes en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>101437</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142874</t>
+          <t>141874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163457</t>
+          <t>163218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>213819</t>
+          <t>211750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>277264</t>
+          <t>278196</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>343859</t>
+          <t>343690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>888849</t>
+          <t>889849</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>927186</t>
+          <t>930286</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1101294</t>
+          <t>1103363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1151656</t>
+          <t>1151895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2002976</t>
+          <t>2003145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2069571</t>
+          <t>2068639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38048</t>
+          <t>37481</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65673</t>
+          <t>68742</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>22602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45476</t>
+          <t>46931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65926</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100319</t>
+          <t>101875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1627740</t>
+          <t>1624671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1655365</t>
+          <t>1655932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1542197</t>
+          <t>1540742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1565612</t>
+          <t>1565071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3180767</t>
+          <t>3179211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3215160</t>
+          <t>3214560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>21336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32662</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528974</t>
+          <t>530072</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544508</t>
+          <t>544655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>460137</t>
+          <t>459902</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>472501</t>
+          <t>472964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>995158</t>
+          <t>994741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1014067</t>
+          <t>1013927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>158721</t>
+          <t>161041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209270</t>
+          <t>210802</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201267</t>
+          <t>201167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259997</t>
+          <t>258756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>376434</t>
+          <t>380100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>453261</t>
+          <t>455760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3067273</t>
+          <t>3065741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3117822</t>
+          <t>3115502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3119200</t>
+          <t>3120441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3177930</t>
+          <t>3178030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6202480</t>
+          <t>6199981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6279307</t>
+          <t>6275641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2012</t>
+          <t>Población con diagnóstico de diabetes en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145744</t>
+          <t>148640</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198236</t>
+          <t>196161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>218042</t>
+          <t>215460</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>276050</t>
+          <t>274161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>380546</t>
+          <t>375594</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>455095</t>
+          <t>451768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>776407</t>
+          <t>778482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>828899</t>
+          <t>826003</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1061747</t>
+          <t>1063636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1119755</t>
+          <t>1122337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1857345</t>
+          <t>1860672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1931894</t>
+          <t>1936846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57812</t>
+          <t>58171</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93085</t>
+          <t>93252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40956</t>
+          <t>41294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>71313</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106486</t>
+          <t>109595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152462</t>
+          <t>154099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1870872</t>
+          <t>1870705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1906145</t>
+          <t>1905786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1684692</t>
+          <t>1683279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1713636</t>
+          <t>1713298</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3566087</t>
+          <t>3564450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3612063</t>
+          <t>3608954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>23323</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31554</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457864</t>
+          <t>457858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474226</t>
+          <t>474389</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443005</t>
+          <t>443656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455568</t>
+          <t>455657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>908259</t>
+          <t>908755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>928073</t>
+          <t>927849</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>225416</t>
+          <t>226570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>289543</t>
+          <t>291724</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>274791</t>
+          <t>274832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>341625</t>
+          <t>342613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>519801</t>
+          <t>524188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>609870</t>
+          <t>608311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3130239</t>
+          <t>3128058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3194366</t>
+          <t>3193212</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3209395</t>
+          <t>3208407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3276229</t>
+          <t>3276188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6360931</t>
+          <t>6362490</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6451000</t>
+          <t>6446613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2016</t>
+          <t>Población con diagnóstico de diabetes en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129665</t>
+          <t>130410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172428</t>
+          <t>175377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>171145</t>
+          <t>170027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>227247</t>
+          <t>223907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>310369</t>
+          <t>311558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>382148</t>
+          <t>380974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>581919</t>
+          <t>578970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>624682</t>
+          <t>623937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>767413</t>
+          <t>770753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>823515</t>
+          <t>824633</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1366859</t>
+          <t>1368033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1438638</t>
+          <t>1437449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104154</t>
+          <t>103045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148019</t>
+          <t>148999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68517</t>
+          <t>66631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108088</t>
+          <t>106906</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>181853</t>
+          <t>180539</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>240294</t>
+          <t>238759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1928366</t>
+          <t>1927386</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1972231</t>
+          <t>1973340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1880212</t>
+          <t>1881394</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1919783</t>
+          <t>1921669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3824391</t>
+          <t>3825926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3882832</t>
+          <t>3884146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35962</t>
+          <t>38683</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23531</t>
+          <t>23919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>26715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55088</t>
+          <t>53211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510924</t>
+          <t>508203</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531572</t>
+          <t>531586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525609</t>
+          <t>525221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541119</t>
+          <t>541678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1040939</t>
+          <t>1042816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1068779</t>
+          <t>1069312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264826</t>
+          <t>265638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>329799</t>
+          <t>329530</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>263034</t>
+          <t>263054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>335537</t>
+          <t>332564</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>544304</t>
+          <t>547114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>639471</t>
+          <t>642085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3047819</t>
+          <t>3048088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3112792</t>
+          <t>3111980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3196563</t>
+          <t>3199536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3269066</t>
+          <t>3269046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6270247</t>
+          <t>6267633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6365414</t>
+          <t>6362604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2023</t>
+          <t>Población con diagnóstico de diabetes en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85862</t>
+          <t>85298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116293</t>
+          <t>115609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>142072</t>
+          <t>142352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174102</t>
+          <t>173424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>238232</t>
+          <t>238141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>279658</t>
+          <t>283128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396226</t>
+          <t>396910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426657</t>
+          <t>427221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>578454</t>
+          <t>579132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>610484</t>
+          <t>610204</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>985417</t>
+          <t>981947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1026843</t>
+          <t>1026934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109254</t>
+          <t>109661</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>186143</t>
+          <t>187513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63914</t>
+          <t>63221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105667</t>
+          <t>105814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194235</t>
+          <t>196401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>283685</t>
+          <t>281302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2098786</t>
+          <t>2097416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2175675</t>
+          <t>2175268</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2129829</t>
+          <t>2129682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2171582</t>
+          <t>2172275</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4236740</t>
+          <t>4239123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4326190</t>
+          <t>4324024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31625</t>
+          <t>32429</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56598</t>
+          <t>57230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>25334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>50576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76661</t>
+          <t>77477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590025</t>
+          <t>589393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614998</t>
+          <t>614194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635033</t>
+          <t>635129</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647971</t>
+          <t>647578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1230425</t>
+          <t>1229609</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1259035</t>
+          <t>1256510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>232601</t>
+          <t>231941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>337087</t>
+          <t>337247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216329</t>
+          <t>223026</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288327</t>
+          <t>294703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>483513</t>
+          <t>483054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>613205</t>
+          <t>616219</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3106985</t>
+          <t>3106825</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3211471</t>
+          <t>3212131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3360188</t>
+          <t>3353812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3432186</t>
+          <t>3425489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6479381</t>
+          <t>6476367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6609073</t>
+          <t>6609532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1402-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1402-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101437</t>
+          <t>102070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141874</t>
+          <t>144173</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163218</t>
+          <t>163080</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>211750</t>
+          <t>216321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>278196</t>
+          <t>280535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>343690</t>
+          <t>343340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>889849</t>
+          <t>887550</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>930286</t>
+          <t>929653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1103363</t>
+          <t>1098792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1151895</t>
+          <t>1152033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2003145</t>
+          <t>2003495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2068639</t>
+          <t>2066300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37481</t>
+          <t>37879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68742</t>
+          <t>65447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>45056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>65786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101875</t>
+          <t>105047</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1624671</t>
+          <t>1627966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1655932</t>
+          <t>1655534</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1540742</t>
+          <t>1542617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1565071</t>
+          <t>1564775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3179211</t>
+          <t>3176039</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3214560</t>
+          <t>3215300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13893</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33079</t>
+          <t>31267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530072</t>
+          <t>528639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544655</t>
+          <t>544587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>459902</t>
+          <t>461175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>472964</t>
+          <t>472522</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>994741</t>
+          <t>996553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1013927</t>
+          <t>1014378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>161041</t>
+          <t>163060</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>210802</t>
+          <t>212361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201167</t>
+          <t>201539</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258756</t>
+          <t>255318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>380100</t>
+          <t>377762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>455760</t>
+          <t>457589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3065741</t>
+          <t>3064182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3115502</t>
+          <t>3113483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3120441</t>
+          <t>3123879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3178030</t>
+          <t>3177658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6199981</t>
+          <t>6198152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6275641</t>
+          <t>6277979</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148640</t>
+          <t>147949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>196161</t>
+          <t>196685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>215460</t>
+          <t>218117</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>274161</t>
+          <t>273603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>375594</t>
+          <t>383360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>451768</t>
+          <t>456384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>778482</t>
+          <t>777958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>826003</t>
+          <t>826694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1063636</t>
+          <t>1064194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1122337</t>
+          <t>1119680</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1860672</t>
+          <t>1856056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1936846</t>
+          <t>1929080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58171</t>
+          <t>58651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93252</t>
+          <t>93031</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41294</t>
+          <t>40566</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71313</t>
+          <t>70855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109595</t>
+          <t>105868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154099</t>
+          <t>152863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1870705</t>
+          <t>1870926</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1905786</t>
+          <t>1905306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1683279</t>
+          <t>1683737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1713298</t>
+          <t>1714026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3564450</t>
+          <t>3565686</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3608954</t>
+          <t>3612681</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23323</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>15073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11964</t>
+          <t>11971</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31058</t>
+          <t>31921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457858</t>
+          <t>458676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474389</t>
+          <t>474423</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443656</t>
+          <t>443558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455657</t>
+          <t>455661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>908755</t>
+          <t>907892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>927849</t>
+          <t>927842</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>226570</t>
+          <t>224177</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>291724</t>
+          <t>287151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>274832</t>
+          <t>271121</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>342613</t>
+          <t>341697</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>524188</t>
+          <t>520162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>608311</t>
+          <t>614191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3128058</t>
+          <t>3132631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3193212</t>
+          <t>3195605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3208407</t>
+          <t>3209323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3276188</t>
+          <t>3279899</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6362490</t>
+          <t>6356610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6446613</t>
+          <t>6450639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130410</t>
+          <t>129744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>175377</t>
+          <t>170985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170027</t>
+          <t>170805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223907</t>
+          <t>225009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>311558</t>
+          <t>312071</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>380974</t>
+          <t>381403</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>578970</t>
+          <t>583362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>623937</t>
+          <t>624603</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>770753</t>
+          <t>769651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>824633</t>
+          <t>823855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1368033</t>
+          <t>1367604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1437449</t>
+          <t>1436936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103045</t>
+          <t>103567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148999</t>
+          <t>147605</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t>66686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106906</t>
+          <t>106380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180539</t>
+          <t>181562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238759</t>
+          <t>239508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1927386</t>
+          <t>1928780</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1973340</t>
+          <t>1972818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1881394</t>
+          <t>1881920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1921669</t>
+          <t>1921614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3825926</t>
+          <t>3825177</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3884146</t>
+          <t>3883123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>15092</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38683</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23919</t>
+          <t>23001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26715</t>
+          <t>26806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53211</t>
+          <t>54870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508203</t>
+          <t>509497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531586</t>
+          <t>531794</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525221</t>
+          <t>526139</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541678</t>
+          <t>540921</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1042816</t>
+          <t>1041157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069312</t>
+          <t>1069221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>265638</t>
+          <t>266690</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>329530</t>
+          <t>333655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>263054</t>
+          <t>263632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332564</t>
+          <t>334796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>547114</t>
+          <t>553172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>642085</t>
+          <t>648791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3048088</t>
+          <t>3043963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3111980</t>
+          <t>3110928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3199536</t>
+          <t>3197304</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3269046</t>
+          <t>3268468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6267633</t>
+          <t>6260927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6362604</t>
+          <t>6356546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100149</t>
+          <t>108030</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85298</t>
+          <t>92498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115609</t>
+          <t>125409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>157625</t>
+          <t>171071</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>142352</t>
+          <t>154086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173424</t>
+          <t>187775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>257774</t>
+          <t>279102</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>238141</t>
+          <t>255167</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283128</t>
+          <t>302183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>412370</t>
+          <t>467896</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396910</t>
+          <t>450517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427221</t>
+          <t>483428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>594931</t>
+          <t>649556</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>579132</t>
+          <t>632852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>610204</t>
+          <t>666541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1007301</t>
+          <t>1117452</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>981947</t>
+          <t>1094371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1026934</t>
+          <t>1141387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512519</t>
+          <t>575926</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512519</t>
+          <t>575926</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512519</t>
+          <t>575926</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752556</t>
+          <t>820627</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752556</t>
+          <t>820627</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752556</t>
+          <t>820627</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265075</t>
+          <t>1396554</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265075</t>
+          <t>1396554</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265075</t>
+          <t>1396554</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>155737</t>
+          <t>169777</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109661</t>
+          <t>147872</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>187513</t>
+          <t>193379</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87741</t>
+          <t>98867</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63221</t>
+          <t>85548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105814</t>
+          <t>114417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>243478</t>
+          <t>268644</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196401</t>
+          <t>243211</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>281302</t>
+          <t>296825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2129192</t>
+          <t>2055502</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2097416</t>
+          <t>2031900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2175268</t>
+          <t>2077407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2147755</t>
+          <t>2070105</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2129682</t>
+          <t>2054555</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2172275</t>
+          <t>2083424</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4276947</t>
+          <t>4125606</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4239123</t>
+          <t>4097425</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4324024</t>
+          <t>4151039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2284929</t>
+          <t>2225279</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2284929</t>
+          <t>2225279</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2284929</t>
+          <t>2225279</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235496</t>
+          <t>2168972</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235496</t>
+          <t>2168972</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235496</t>
+          <t>2168972</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4520425</t>
+          <t>4394250</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4520425</t>
+          <t>4394250</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4520425</t>
+          <t>4394250</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43362</t>
+          <t>49685</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>37516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57230</t>
+          <t>64784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25334</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>61226</t>
+          <t>70892</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50576</t>
+          <t>55922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77477</t>
+          <t>87239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>603261</t>
+          <t>661902</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>589393</t>
+          <t>646803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614194</t>
+          <t>674071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>642600</t>
+          <t>713670</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635129</t>
+          <t>705615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647578</t>
+          <t>720402</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,27 +6406,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1245860</t>
+          <t>1375572</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1229609</t>
+          <t>1359225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1256510</t>
+          <t>1390542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>299249</t>
+          <t>327493</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>231941</t>
+          <t>297294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>337247</t>
+          <t>358773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>263229</t>
+          <t>291145</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>223026</t>
+          <t>267861</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>294703</t>
+          <t>315974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>562478</t>
+          <t>618638</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>483054</t>
+          <t>579007</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>616219</t>
+          <t>658292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3144823</t>
+          <t>3185299</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3106825</t>
+          <t>3154019</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3212131</t>
+          <t>3215498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3385286</t>
+          <t>3433332</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3353812</t>
+          <t>3408503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3425489</t>
+          <t>3456616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6530108</t>
+          <t>6618630</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6476367</t>
+          <t>6578976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6609532</t>
+          <t>6658261</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3444072</t>
+          <t>3512792</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3444072</t>
+          <t>3512792</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3444072</t>
+          <t>3512792</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3648515</t>
+          <t>3724477</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3648515</t>
+          <t>3724477</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3648515</t>
+          <t>3724477</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7092586</t>
+          <t>7237268</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7092586</t>
+          <t>7237268</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7092586</t>
+          <t>7237268</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
